--- a/backtest_runs/20260410_193731/by_symbol/FASM/FASM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/FASM/FASM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>127582.45</v>
@@ -1090,10 +1090,10 @@
         </is>
       </c>
       <c r="I14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>127582.45</v>
@@ -1139,7 +1139,7 @@
         <v>-609.7299999999934</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>126972.72</v>
@@ -1231,7 +1231,7 @@
         <v>-8943.510000000004</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>118029.21</v>
@@ -1507,7 +1507,7 @@
         <v>-3964.449999999997</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>117571.31</v>
@@ -1599,7 +1599,7 @@
         <v>-3306.519999999993</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="2" t="n">
         <v>114264.79</v>
